--- a/data/trans_camb/P0901-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 2,01</t>
+          <t>-5,3; 1,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,88</t>
+          <t>-2,5; 5,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 3,77</t>
+          <t>-3,4; 3,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 4,2</t>
+          <t>-6,66; 4,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 4,9</t>
+          <t>-5,37; 5,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 4,55</t>
+          <t>-4,92; 4,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,72</t>
+          <t>-4,42; 1,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,19</t>
+          <t>-2,24; 4,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,03</t>
+          <t>-2,55; 3,37</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,5; 35,87</t>
+          <t>-54,3; 26,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 98,24</t>
+          <t>-25,97; 88,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 61,49</t>
+          <t>-34,86; 63,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 42,75</t>
+          <t>-44,3; 39,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 47,19</t>
+          <t>-36,41; 49,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 45,47</t>
+          <t>-30,83; 44,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 21,77</t>
+          <t>-39,25; 16,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 50,94</t>
+          <t>-19,05; 53,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 36,97</t>
+          <t>-21,71; 42,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,96</t>
+          <t>2,74; 11,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 4,95</t>
+          <t>-1,8; 5,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,66</t>
+          <t>1,53; 9,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 7,11</t>
+          <t>-2,91; 6,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 5,92</t>
+          <t>-3,36; 5,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 8,12</t>
+          <t>0,06; 8,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,83</t>
+          <t>0,97; 7,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,47</t>
+          <t>-1,45; 4,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,55</t>
+          <t>1,92; 7,45</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,25; 289,44</t>
+          <t>34,18; 338,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 130,55</t>
+          <t>-27,33; 158,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,69; 246,59</t>
+          <t>18,01; 291,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 89,81</t>
+          <t>-26,32; 86,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 75,47</t>
+          <t>-28,22; 77,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 106,38</t>
+          <t>-0,58; 119,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 126,7</t>
+          <t>9,56; 111,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 69,75</t>
+          <t>-16,37; 71,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,85; 123,73</t>
+          <t>19,54; 117,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 8,45</t>
+          <t>0,38; 8,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 4,2</t>
+          <t>-3,42; 4,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 7,74</t>
+          <t>-7,85; 7,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 7,15</t>
+          <t>-9,33; 7,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 9,86</t>
+          <t>-9,01; 10,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 11,37</t>
+          <t>-4,69; 12,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 7,09</t>
+          <t>-0,27; 6,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 4,27</t>
+          <t>-3,26; 3,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 7,47</t>
+          <t>-8,99; 6,89</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 106,18</t>
+          <t>2,23; 99,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 53,83</t>
+          <t>-29,23; 50,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,59; 83,74</t>
+          <t>-66,3; 84,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 40,66</t>
+          <t>-35,0; 43,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 58,85</t>
+          <t>-34,25; 63,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 63,19</t>
+          <t>-18,27; 73,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 66,77</t>
+          <t>-2,5; 63,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 39,05</t>
+          <t>-23,3; 36,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 61,84</t>
+          <t>-61,19; 56,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,32</t>
+          <t>0,35; 6,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,37</t>
+          <t>-1,83; 3,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,63</t>
+          <t>3,64; 9,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 4,59</t>
+          <t>-2,69; 4,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,93</t>
+          <t>-3,4; 4,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 3,85</t>
+          <t>-9,03; 3,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,65</t>
+          <t>0,26; 4,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,05</t>
+          <t>-1,3; 3,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 5,94</t>
+          <t>-1,3; 6,06</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,15; 65,06</t>
+          <t>2,71; 62,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 34,73</t>
+          <t>-15,05; 34,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,61; 94,89</t>
+          <t>29,96; 97,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 36,26</t>
+          <t>-15,78; 38,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 31,32</t>
+          <t>-20,83; 30,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 28,55</t>
+          <t>-55,74; 27,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,32; 41,9</t>
+          <t>1,91; 40,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 27,98</t>
+          <t>-9,64; 26,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 51,95</t>
+          <t>-7,54; 51,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 6,54</t>
+          <t>-2,32; 6,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 7,53</t>
+          <t>-1,46; 7,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 12,78</t>
+          <t>2,97; 13,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,78; 17,1</t>
+          <t>7,51; 16,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,9; 13,54</t>
+          <t>4,76; 13,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 14,02</t>
+          <t>1,46; 13,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 11,24</t>
+          <t>4,53; 11,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,47</t>
+          <t>2,89; 9,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,56; 12,42</t>
+          <t>3,68; 12,24</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 70,83</t>
+          <t>-17,55; 74,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 79,36</t>
+          <t>-9,66; 88,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21,68; 143,09</t>
+          <t>20,72; 146,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43,63; 129,33</t>
+          <t>41,04; 126,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,76; 102,01</t>
+          <t>25,35; 105,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,87; 101,44</t>
+          <t>11,41; 106,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,94; 91,37</t>
+          <t>28,14; 94,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19,84; 76,08</t>
+          <t>17,69; 79,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30,82; 99,35</t>
+          <t>25,39; 99,94</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 5,03</t>
+          <t>-1,15; 5,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,67</t>
+          <t>-3,14; 2,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,11</t>
+          <t>-3,45; 2,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,71</t>
+          <t>1,62; 8,54</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,77</t>
+          <t>0,66; 7,75</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,83</t>
+          <t>2,27; 9,15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,11</t>
+          <t>1,45; 7,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 6,0</t>
+          <t>0,19; 6,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,32; 6,09</t>
+          <t>0,58; 6,46</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 267,94</t>
+          <t>-38,21; 274,92</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-71,77; 145,1</t>
+          <t>-68,34; 167,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,35; 136,47</t>
+          <t>-71,93; 159,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8,27; 48,43</t>
+          <t>7,06; 47,05</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,7; 42,96</t>
+          <t>3,21; 43,09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,83; 49,13</t>
+          <t>10,56; 51,47</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,55; 47,94</t>
+          <t>7,89; 48,05</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 39,7</t>
+          <t>1,03; 41,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1,18; 40,82</t>
+          <t>3,35; 43,26</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,42</t>
+          <t>1,42; 4,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,94</t>
+          <t>-0,05; 2,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,59</t>
+          <t>0,75; 5,54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,45</t>
+          <t>2,59; 6,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,14</t>
+          <t>1,11; 4,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,11</t>
+          <t>-0,71; 5,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,05</t>
+          <t>2,5; 4,89</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,49</t>
+          <t>1,05; 3,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,88</t>
+          <t>1,18; 4,99</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15,16; 53,52</t>
+          <t>14,24; 53,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 35,1</t>
+          <t>-0,27; 34,37</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8,93; 65,4</t>
+          <t>8,86; 66,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15,1; 42,74</t>
+          <t>14,85; 41,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,76; 32,76</t>
+          <t>6,43; 31,64</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 33,36</t>
+          <t>-3,52; 32,71</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,57; 41,58</t>
+          <t>18,66; 39,9</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,92; 28,92</t>
+          <t>8,13; 29,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,18; 39,56</t>
+          <t>9,01; 40,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0901-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,59</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 1,6</t>
+          <t>-6,0; 1,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 5,44</t>
+          <t>-2,18; 5,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 3,8</t>
+          <t>-3,32; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 4,26</t>
+          <t>-6,5; 4,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 5,03</t>
+          <t>-5,96; 5,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,46</t>
+          <t>-4,69; 4,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,4</t>
+          <t>-4,03; 1,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,46</t>
+          <t>-2,26; 3,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,37</t>
+          <t>-2,4; 3,49</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,13%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,3; 26,65</t>
+          <t>-56,75; 22,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 88,07</t>
+          <t>-23,07; 93,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 63,92</t>
+          <t>-33,33; 57,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,3; 39,33</t>
+          <t>-40,53; 39,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 49,22</t>
+          <t>-38,13; 51,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 44,42</t>
+          <t>-28,71; 46,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 16,78</t>
+          <t>-36,9; 18,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 53,86</t>
+          <t>-20,52; 46,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 42,17</t>
+          <t>-20,51; 41,13</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>4,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 11,52</t>
+          <t>2,65; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,29</t>
+          <t>-1,91; 5,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,29</t>
+          <t>1,71; 8,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 6,76</t>
+          <t>-3,52; 7,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 5,97</t>
+          <t>-3,32; 6,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 8,62</t>
+          <t>0,67; 8,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 7,31</t>
+          <t>1,46; 7,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,36</t>
+          <t>-1,39; 4,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,45</t>
+          <t>2,1; 7,48</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100,5%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,18; 338,43</t>
+          <t>36,76; 309,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 158,56</t>
+          <t>-30,62; 149,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,01; 291,62</t>
+          <t>17,91; 245,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 86,0</t>
+          <t>-29,47; 88,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 77,81</t>
+          <t>-28,35; 79,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 119,23</t>
+          <t>4,7; 114,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 111,4</t>
+          <t>17,4; 121,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 71,17</t>
+          <t>-15,86; 75,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 117,33</t>
+          <t>22,86; 119,46</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>5,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 8,25</t>
+          <t>0,28; 8,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 4,06</t>
+          <t>-3,56; 4,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 7,64</t>
+          <t>1,11; 9,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 7,23</t>
+          <t>-9,32; 7,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 10,28</t>
+          <t>-9,77; 9,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 12,48</t>
+          <t>-5,71; 12,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,81</t>
+          <t>-0,22; 7,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,97</t>
+          <t>-3,04; 4,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 6,89</t>
+          <t>1,73; 9,43</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 99,45</t>
+          <t>0,76; 108,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 50,95</t>
+          <t>-30,05; 51,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,3; 84,03</t>
+          <t>10,62; 123,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 43,58</t>
+          <t>-34,89; 44,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 63,85</t>
+          <t>-37,69; 54,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 73,51</t>
+          <t>-21,32; 69,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 63,04</t>
+          <t>-3,02; 66,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 36,25</t>
+          <t>-21,28; 41,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,19; 56,71</t>
+          <t>12,68; 90,57</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>6,4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>5,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 6,27</t>
+          <t>0,41; 5,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,46</t>
+          <t>-1,76; 3,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,5</t>
+          <t>3,82; 9,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 4,92</t>
+          <t>-3,0; 4,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 4,0</t>
+          <t>-3,39; 4,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 3,8</t>
+          <t>-0,93; 6,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,61</t>
+          <t>0,14; 4,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,01</t>
+          <t>-1,31; 3,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,06</t>
+          <t>2,95; 7,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,71%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>41,41%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 62,44</t>
+          <t>2,49; 57,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 34,44</t>
+          <t>-15,01; 34,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,96; 97,16</t>
+          <t>31,01; 96,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 38,2</t>
+          <t>-18,05; 36,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 30,42</t>
+          <t>-21,21; 31,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,74; 27,3</t>
+          <t>-5,86; 49,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 40,65</t>
+          <t>0,87; 40,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 26,74</t>
+          <t>-10,11; 27,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 51,44</t>
+          <t>21,59; 65,47</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,81</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,04</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,68</t>
+          <t>9,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,62</t>
+          <t>-2,56; 6,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 7,36</t>
+          <t>-1,18; 7,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,97; 13,05</t>
+          <t>0,82; 10,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,51; 16,83</t>
+          <t>7,65; 17,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,76; 13,86</t>
+          <t>4,65; 13,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,88</t>
+          <t>7,36; 15,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 11,79</t>
+          <t>4,94; 11,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,74</t>
+          <t>2,9; 9,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,24</t>
+          <t>6,07; 12,01</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>64,79%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 74,05</t>
+          <t>-19,0; 77,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 88,34</t>
+          <t>-8,25; 86,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20,72; 146,79</t>
+          <t>5,73; 124,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41,04; 126,75</t>
+          <t>40,43; 122,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>25,35; 105,92</t>
+          <t>26,16; 102,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,41; 106,56</t>
+          <t>39,98; 113,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,14; 94,8</t>
+          <t>31,45; 99,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,69; 79,78</t>
+          <t>18,79; 77,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25,39; 99,94</t>
+          <t>36,79; 98,7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,58</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>3,48</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,43</t>
+          <t>-1,53; 5,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,78</t>
+          <t>-3,29; 2,74</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,4</t>
+          <t>-3,37; 2,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,54</t>
+          <t>1,79; 8,59</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,75</t>
+          <t>0,8; 7,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,15</t>
+          <t>1,92; 8,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,45</t>
+          <t>1,57; 7,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,19; 6,15</t>
+          <t>-0,25; 5,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,46</t>
+          <t>0,67; 6,2</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-20,97%</t>
+          <t>-21,89%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-38,21; 274,92</t>
+          <t>-39,16; 271,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,34; 167,02</t>
+          <t>-71,19; 155,09</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 159,01</t>
+          <t>-73,62; 129,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,06; 47,05</t>
+          <t>8,43; 47,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,21; 43,09</t>
+          <t>4,53; 43,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,56; 51,47</t>
+          <t>8,7; 48,15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,89; 48,05</t>
+          <t>8,78; 46,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1,03; 41,06</t>
+          <t>-1,48; 39,34</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,35; 43,26</t>
+          <t>3,82; 41,28</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>4,53</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,39</t>
+          <t>4,59</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,48</t>
+          <t>1,52; 4,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,84</t>
+          <t>-0,03; 2,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,54</t>
+          <t>3,15; 6,18</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,46</t>
+          <t>2,55; 6,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,87</t>
+          <t>1,28; 5,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 5,13</t>
+          <t>2,9; 6,11</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,89</t>
+          <t>2,44; 4,98</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,58</t>
+          <t>1,06; 3,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,99</t>
+          <t>3,32; 5,73</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,24; 53,8</t>
+          <t>16,21; 55,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 34,37</t>
+          <t>-0,37; 35,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8,86; 66,19</t>
+          <t>33,09; 76,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,85; 41,52</t>
+          <t>14,6; 41,03</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,43; 31,64</t>
+          <t>7,29; 32,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 32,71</t>
+          <t>17,18; 39,77</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,66; 39,9</t>
+          <t>18,47; 41,26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,13; 29,31</t>
+          <t>7,62; 29,01</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,01; 40,7</t>
+          <t>25,1; 47,13</t>
         </is>
       </c>
     </row>
